--- a/advantest/dist/20261028_Advantest個股模型_v0.4.xlsx
+++ b/advantest/dist/20261028_Advantest個股模型_v0.4.xlsx
@@ -10023,26 +10023,45 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Advantest FY2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">簡報（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-04-27</t>
+      <t xml:space="preserve">Advantest FY2026 Q1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">決算說明（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-07-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，公司原文 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JE_BIZ_260729_note</t>
     </r>
     <r>
       <rPr>
@@ -10061,16 +10080,92 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10.5–11.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（二手轉述，搜尋摘錄；公司原文未開啟）</t>
+      <t xml:space="preserve">CY2026 SoC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">測試機市場上修至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">105–115 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億美元（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4/27 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">簡報為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">87–95 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源複核開啟原文）</t>
     </r>
   </si>
   <si>
@@ -10189,39 +10284,48 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Advantest</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.5–3.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（公司原文未開啟，二手摘錄）</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同上（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-07-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公司原文）：記憶體測試機市場上修至 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25–30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">億美元</t>
     </r>
   </si>
   <si>
@@ -46856,7 +46960,7 @@
       <c r="G48" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H48" s="8" t="s">
+      <c r="H48" s="5" t="s">
         <v>166</v>
       </c>
       <c r="I48" s="5" t="s">

--- a/advantest/dist/20261028_Advantest個股模型_v0.4.xlsx
+++ b/advantest/dist/20261028_Advantest個股模型_v0.4.xlsx
@@ -13678,26 +13678,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -14268,26 +14268,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -14723,26 +14723,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261025_SK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海力士模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.5.1.xlsx</t>
+      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.6.xlsx</t>
     </r>
     <r>
       <rPr>

--- a/advantest/dist/20261028_Advantest個股模型_v0.4.xlsx
+++ b/advantest/dist/20261028_Advantest個股模型_v0.4.xlsx
@@ -5104,7 +5104,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -5123,7 +5123,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5397,7 +5397,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -5416,7 +5416,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5694,7 +5694,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -5713,7 +5713,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5845,7 +5845,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -5864,7 +5864,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6016,7 +6016,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6035,7 +6035,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6167,7 +6167,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6186,7 +6186,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6329,7 +6329,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6348,7 +6348,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6556,7 +6556,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6575,7 +6575,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6768,7 +6768,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6787,7 +6787,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6919,7 +6919,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -6938,7 +6938,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7176,7 +7176,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7195,7 +7195,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7327,7 +7327,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7346,7 +7346,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7489,7 +7489,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7508,7 +7508,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7640,7 +7640,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7659,7 +7659,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7880,7 +7880,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -7899,7 +7899,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8248,7 +8248,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8267,7 +8267,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8372,7 +8372,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8391,7 +8391,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8571,7 +8571,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8590,7 +8590,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8692,7 +8692,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8711,7 +8711,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8813,7 +8813,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8832,7 +8832,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -8934,7 +8934,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -8953,7 +8953,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -9055,7 +9055,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261028_</t>
+      <t xml:space="preserve">tsmc/dist/20261030_</t>
     </r>
     <r>
       <rPr>
@@ -9074,7 +9074,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13234,7 +13234,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -13253,7 +13253,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -13824,7 +13824,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -13843,7 +13843,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -14279,7 +14279,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">skhynix/dist/20261029_SK</t>
+      <t xml:space="preserve">skhynix/dist/20261030_SK</t>
     </r>
     <r>
       <rPr>
@@ -14298,7 +14298,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.6.xlsx</t>
+      <t xml:space="preserve">_v0.6.1.xlsx</t>
     </r>
     <r>
       <rPr>
